--- a/downloads/contracosta.xlsx
+++ b/downloads/contracosta.xlsx
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Contra Costa chiropractors, shared spaces and practitioners</t>
+          <t>Contra Costa chiropractors and shared offices</t>
         </is>
       </c>
     </row>

--- a/downloads/contracosta.xlsx
+++ b/downloads/contracosta.xlsx
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Contra Costa chiropractors and shared offices</t>
+          <t>Contra Costa County chiropractors and shared offices</t>
         </is>
       </c>
     </row>

--- a/downloads/contracosta.xlsx
+++ b/downloads/contracosta.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chiropractors licensed in Contr" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shared spaces buildings where t" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shared spaces addresses where t" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chiropractors whose Board addre" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unincorporated Medical, Dental" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chiropractic building permits i" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contra Costa chiropractors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buildings with 2+ chiros" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Addresses with 2+ practitioners" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chiros at home addresses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medical-dental parcels" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chiropractic building permits" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +490,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Chiropractors licensed in Contr</t>
+          <t>Contra Costa chiropractors</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -505,7 +505,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Shared spaces buildings where t</t>
+          <t>Buildings with 2+ chiros</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -520,7 +520,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Shared spaces addresses where t</t>
+          <t>Addresses with 2+ practitioners</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -535,7 +535,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Chiropractors whose Board addre</t>
+          <t>Chiros at home addresses</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -550,7 +550,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Unincorporated Medical, Dental</t>
+          <t>Medical-dental parcels</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -565,7 +565,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Chiropractic building permits i</t>
+          <t>Chiropractic building permits</t>
         </is>
       </c>
       <c r="B10" t="n">
